--- a/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30879F40-4942-407A-B5AF-4300EF6F3AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B731974-3635-41D2-98FD-51D2D900B2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1404,7 +1404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CCEF76D-04BC-4EB5-99D6-3D29D1E2D337}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FFA601-37DC-4822-BA70-71528EFD09C9}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1461,7 +1461,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B8D00B1-46E0-4F13-8769-505430AB3827}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10BF4E40-C4C0-4E3D-8E0F-7F842A3EDBB9}">
   <dimension ref="B9:O44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2503,7 +2503,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2780C50-B140-4833-AA0D-854E8F38AA06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB46996-60BF-431B-99E6-656380CB739E}">
   <dimension ref="B9:T86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4840,7 +4840,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23347435-DCD8-4C21-80EB-050BECC51E4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E55AEA5-97E9-4ABA-894A-1FBDD1DC7E91}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4884,7 +4884,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A68CC97-3C13-4991-AD0E-6A7B5CD9CC0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C973116-5CD1-4880-B60C-4DEA8FEBE792}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4933,7 +4933,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06869BA3-E24E-4A1D-9415-FA84E8E490C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD4511C-BED7-4D79-9FFB-BF9B74EFA2FB}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4971,7 +4971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB219D8-4553-46A2-9B55-D002293DE880}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E371D011-9130-4A79-8464-6A233AEDA66B}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5017,7 +5017,7 @@
         <v>37</v>
       </c>
       <c r="D12">
-        <v>0.16795833333333335</v>
+        <v>0.16795833333333332</v>
       </c>
       <c r="E12" t="s">
         <v>219</v>
@@ -5087,7 +5087,7 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>0.33138333333333336</v>
+        <v>0.33138333333333331</v>
       </c>
       <c r="E17" t="s">
         <v>219</v>
@@ -5185,7 +5185,7 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>0.26681666666666665</v>
+        <v>0.2668166666666667</v>
       </c>
       <c r="E24" t="s">
         <v>219</v>
@@ -5269,7 +5269,7 @@
         <v>37</v>
       </c>
       <c r="D30">
-        <v>0.30453333333333332</v>
+        <v>0.30453333333333338</v>
       </c>
       <c r="E30" t="s">
         <v>219</v>
@@ -5367,7 +5367,7 @@
         <v>37</v>
       </c>
       <c r="D37">
-        <v>0.2971833333333333</v>
+        <v>0.29718333333333335</v>
       </c>
       <c r="E37" t="s">
         <v>219</v>
@@ -5381,7 +5381,7 @@
         <v>37</v>
       </c>
       <c r="D38">
-        <v>0.28041666666666659</v>
+        <v>0.2804166666666667</v>
       </c>
       <c r="E38" t="s">
         <v>219</v>
